--- a/forms/trg/Formulir_TRG_stepmic.xlsx
+++ b/forms/trg/Formulir_TRG_stepmic.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Keahlian anggota banyak yang kosong. Mohon pilih keahlian utama untuk setiap anggota.</t>
+          <t>Data TRG ini relatif lengkap. Mohon periksa dan lengkapi mitra serta riset terbaik.</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B34)</f>
+        <f>COUNTA(Anggota!B5:B35)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F34)</f>
+        <f>COUNTA(Anggota!F5:F35)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,41 +913,37 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Rina Masadah, MD, M.Phil, Ph.D</t>
+          <t>Andi Alfian Zainuddin, MD, MPH, Ph.D</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Pathology</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Community medicine | Health management | Environmental health | Epidemiology</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-1380-4759</t>
-        </is>
-      </c>
+      <c r="J5" s="12" t="n"/>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>5978304</t>
+          <t>6013409</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>55837832600</t>
+          <t>57215695097</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -962,17 +958,17 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Andi Tenri Esa, MD, Ph.D</t>
+          <t>Prof. Rina Masadah, MD, M.Phil, Ph.D</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Allergy Immunology | Endocrine Metabolic | Cardiovascular</t>
+          <t>Pathology</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -986,17 +982,17 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-8373-6755</t>
+          <t>0000-0002-1380-4759</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6710829</t>
+          <t>5978304</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>6507386274</t>
+          <t>55837832600</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1011,27 +1007,43 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Andi Afdal Abdullah, MD, MBA, Ph.D</t>
+          <t>Andi Tenri Esa, MD, Ph.D</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
+          <t>Allergy Immunology | Endocrine Metabolic | Cardiovascular</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E7" s="11" t="n"/>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-8373-6755</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>6710829</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>6507386274</t>
+        </is>
+      </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1044,39 +1056,27 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Firdaus Hamid, MD, Ph.D</t>
+          <t>Andi Afdal Abdullah, MD, MBA, Ph.D</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Immunology | Microbiology | Parasitology | Medicine | Epidemiology</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
           <t>Hasanuddin University</t>
         </is>
       </c>
+      <c r="E8" s="11" t="n"/>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="12" t="n"/>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>5999920</t>
-        </is>
-      </c>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>35933184500</t>
-        </is>
-      </c>
+      <c r="K8" s="12" t="n"/>
+      <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1089,17 +1089,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Agussalim Bukhari, MD, M.Clin.Nut, Ph.D</t>
+          <t>Prof. Firdaus Hamid, MD, Ph.D</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Insulin Resistance | Obesity | Molecular Biology | Clinical Nutrition | Immunology</t>
+          <t>Immunology | Microbiology | Parasitology | Medicine | Epidemiology</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -1114,12 +1114,12 @@
       <c r="J9" s="12" t="n"/>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>6043333</t>
+          <t>5999920</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>16024065100</t>
+          <t>35933184500</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Haerani Rasyid, MD, Ph.D</t>
+          <t>Prof. Agussalim Bukhari, MD, M.Clin.Nut, Ph.D</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Clinical Nutrition | Nephrology-Hypertension | Internal Medicine</t>
+          <t>Insulin Resistance | Obesity | Molecular Biology | Clinical Nutrition | Immunology</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -1156,19 +1156,15 @@
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-7404-2973</t>
-        </is>
-      </c>
+      <c r="J10" s="12" t="n"/>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>6007114</t>
+          <t>6043333</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>55749052100</t>
+          <t>16024065100</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1183,17 +1179,17 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Irawan Yusuf, Ph.D</t>
+          <t>Prof. Haerani Rasyid, MD, Ph.D</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Physiology | Genetic Medicine</t>
+          <t>Clinical Nutrition | Nephrology-Hypertension | Internal Medicine</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -1207,17 +1203,17 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-9891-131X</t>
+          <t>0000-0001-7404-2973</t>
         </is>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
-          <t>6652873</t>
+          <t>6007114</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>8109514400</t>
+          <t>55749052100</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1232,22 +1228,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Prof Yuming Guo, Ph.D</t>
+          <t>Prof. Irawan Yusuf, Ph.D</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Air Pollution | Biostatistics | Climate Change | Environmental | Epidemiology</t>
+          <t>Physiology | Genetic Medicine</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Monash University, Australia</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1256,13 +1252,17 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-1766-6592</t>
-        </is>
-      </c>
-      <c r="K12" s="12" t="n"/>
+          <t>0000-0001-9891-131X</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
+        <is>
+          <t>6652873</t>
+        </is>
+      </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>55712472800</t>
+          <t>8109514400</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1277,22 +1277,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Prof. Takuro Furusawa, Ph.D</t>
+          <t>Prof Yuming Guo, Ph.D</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Human Ecology | Area Studies | Human Genetics</t>
+          <t>Air Pollution | Biostatistics | Climate Change | Environmental | Epidemiology</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Kyoto University, Japan</t>
+          <t>Monash University, Australia</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1301,13 +1301,13 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-7772-3053</t>
+          <t>0000-0002-1766-6592</t>
         </is>
       </c>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>7101777627</t>
+          <t>55712472800</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1322,27 +1322,39 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Muh. Firdaus Kasim, MD, M.Sc, Ph.D</t>
+          <t>Prof. Takuro Furusawa, Ph.D</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="n"/>
+          <t>Human Ecology | Area Studies | Human Genetics</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Kyoto University, Japan</t>
+        </is>
+      </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-7772-3053</t>
+        </is>
+      </c>
       <c r="K14" s="12" t="n"/>
-      <c r="L14" s="12" t="n"/>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>7101777627</t>
+        </is>
+      </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1355,12 +1367,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Nurul Qalby, MD</t>
+          <t>Muh. Firdaus Kasim, MD, M.Sc, Ph.D</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1388,12 +1400,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Hedi Kuswanto, B.Sc, M.Sc</t>
+          <t>Nurul Qalby, MD</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1421,12 +1433,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Rais Reskiawan, MD, M.Sc, Ph.D</t>
+          <t>Hedi Kuswanto, B.Sc, M.Sc</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1454,12 +1466,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Sri Ramadhany, MD, MHS, Ph.D</t>
+          <t>Rais Reskiawan, MD, M.Sc, Ph.D</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1487,12 +1499,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Ainan Raena Nas, MD. MPH</t>
+          <t>Sri Ramadhany, MD, MHS, Ph.D</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1520,12 +1532,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Ari Andini Junaedi, MD, MHS</t>
+          <t>Ainan Raena Nas, MD. MPH</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1553,12 +1565,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Djallaluddin</t>
+          <t>Ari Andini Junaedi, MD, MHS</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1586,12 +1598,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Wachyudi Muchsin</t>
+          <t>Djallaluddin</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1617,10 +1629,26 @@
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="11" t="n"/>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Wachyudi Muchsin</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>STEPMIC is a research group dedicated to advancing knowledge in spatial epidemiology and syndemic theory. By integrating geographic information systems (GIS), spatial analysis, and public health data, STEPMIC investigates the relationships between co-occurring health conditions and their social, environmental, and structural determinants</t>
+        </is>
+      </c>
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="12" t="n"/>
       <c r="H23" s="12" t="n"/>
@@ -1628,7 +1656,11 @@
       <c r="J23" s="12" t="n"/>
       <c r="K23" s="12" t="n"/>
       <c r="L23" s="12" t="n"/>
-      <c r="M23" s="12" t="n"/>
+      <c r="M23" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1817,15 +1849,32 @@
       <c r="L34" s="12" t="n"/>
       <c r="M34" s="12" t="n"/>
     </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="12" t="n"/>
+      <c r="H35" s="12" t="n"/>
+      <c r="I35" s="12" t="n"/>
+      <c r="J35" s="12" t="n"/>
+      <c r="K35" s="12" t="n"/>
+      <c r="L35" s="12" t="n"/>
+      <c r="M35" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
